--- a/business_forms/020_no_trespassing_signage_request_form--business_forms.xlsx
+++ b/business_forms/020_no_trespassing_signage_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'building_a'}</t>
+          <t>building_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Building A'}</t>
+          <t>Building A</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'building_b'}</t>
+          <t>building_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Building B'}</t>
+          <t>Building B</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'building_c'}</t>
+          <t>building_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Building C'}</t>
+          <t>Building C</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'hoa_prophets_and_managers'}</t>
+          <t>hoa_prophets_and_managers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'HOA prophets and managers'}</t>
+          <t>HOA prophets and managers</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'facility_team'}</t>
+          <t>facility_team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Facility team'}</t>
+          <t>Facility team</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'property_owner'}</t>
+          <t>property_owner</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Property owner'}</t>
+          <t>Property owner</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'official_no_trespassing_sign'}</t>
+          <t>official_no_trespassing_sign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Official No Trespassing Sign'}</t>
+          <t>Official No Trespassing Sign</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'warning_sign'}</t>
+          <t>warning_sign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Warning Sign'}</t>
+          <t>Warning Sign</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'do_not_enter_sign'}</t>
+          <t>do_not_enter_sign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Do Not Enter Sign'}</t>
+          <t>Do Not Enter Sign</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'pending_prophets_and_managers'}</t>
+          <t>pending_prophets_and_managers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Pending prophets and managers'}</t>
+          <t>Pending prophets and managers</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'facility_team'}</t>
+          <t>facility_team</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Facility team'}</t>
+          <t>Facility team</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'property_owner'}</t>
+          <t>property_owner</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Property owner'}</t>
+          <t>Property owner</t>
         </is>
       </c>
     </row>
